--- a/exports/trend_1d/UJJIVANSFB_full_report.xlsx
+++ b/exports/trend_1d/UJJIVANSFB_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>20.25</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43886</v>
+        <v>43887</v>
       </c>
       <c r="H2" t="n">
-        <v>51.15</v>
+        <v>49.85</v>
       </c>
       <c r="I2" t="n">
         <v>50.45678160977278</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.48</v>
+        <v>-6.91</v>
       </c>
       <c r="L2" t="n">
         <v>9.710000000000001</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.62</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43987</v>
+        <v>43990</v>
       </c>
       <c r="H3" t="n">
-        <v>28.25</v>
+        <v>30.85</v>
       </c>
       <c r="I3" t="n">
         <v>30.29690059093938</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K3" t="n">
-        <v>43.33</v>
+        <v>38.11</v>
       </c>
       <c r="L3" t="n">
         <v>2.81</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>14.93</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44036</v>
+        <v>44039</v>
       </c>
       <c r="H4" t="n">
-        <v>35.3</v>
+        <v>34.2</v>
       </c>
       <c r="I4" t="n">
         <v>34.50621424505729</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K4" t="n">
-        <v>14.42</v>
+        <v>10.86</v>
       </c>
       <c r="L4" t="n">
         <v>12.48</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>17.58</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44149</v>
+        <v>44152</v>
       </c>
       <c r="H5" t="n">
-        <v>33.6</v>
+        <v>34.65</v>
       </c>
       <c r="I5" t="n">
         <v>33.86770355159022</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K5" t="n">
-        <v>1.75</v>
+        <v>-1.32</v>
       </c>
       <c r="L5" t="n">
         <v>12.43</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.58</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44217</v>
+        <v>44218</v>
       </c>
       <c r="H6" t="n">
-        <v>38.7</v>
+        <v>37.9</v>
       </c>
       <c r="I6" t="n">
         <v>37.9478451448542</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K6" t="n">
-        <v>11.69</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>4.47</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>13.73</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44330</v>
+        <v>44333</v>
       </c>
       <c r="H7" t="n">
-        <v>29.7</v>
+        <v>30.15</v>
       </c>
       <c r="I7" t="n">
         <v>29.95588141357629</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K7" t="n">
-        <v>21.64</v>
+        <v>20.45</v>
       </c>
       <c r="L7" t="n">
         <v>2.9</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.84</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44399</v>
+        <v>44400</v>
       </c>
       <c r="H8" t="n">
-        <v>29.75</v>
+        <v>29.1</v>
       </c>
       <c r="I8" t="n">
         <v>29.58404253573016</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.33</v>
+        <v>-3.48</v>
       </c>
       <c r="L8" t="n">
         <v>4.81</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>11.44</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44480</v>
+        <v>44481</v>
       </c>
       <c r="H9" t="n">
-        <v>20.8</v>
+        <v>23.05</v>
       </c>
       <c r="I9" t="n">
         <v>21.3201396330699</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K9" t="n">
-        <v>28.52</v>
+        <v>20.79</v>
       </c>
       <c r="L9" t="n">
         <v>2.92</v>
       </c>
       <c r="M9" t="n">
-        <v>2.98</v>
+        <v>4.81</v>
       </c>
       <c r="N9" t="n">
-        <v>9.76</v>
+        <v>10.82</v>
       </c>
       <c r="O9" t="n">
         <v>-2.18</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>12.09</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44510</v>
+        <v>44511</v>
       </c>
       <c r="H10" t="n">
-        <v>21.05</v>
+        <v>20.85</v>
       </c>
       <c r="I10" t="n">
         <v>20.87436183560458</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K10" t="n">
-        <v>-8.68</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>19.74</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>15.62</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44566</v>
+        <v>44567</v>
       </c>
       <c r="H11" t="n">
-        <v>19.85</v>
+        <v>19.95</v>
       </c>
       <c r="I11" t="n">
         <v>19.85203164189907</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>4.32</v>
       </c>
       <c r="L11" t="n">
         <v>2.88</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>10.1</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H12" t="n">
-        <v>19.75</v>
+        <v>18.95</v>
       </c>
       <c r="I12" t="n">
         <v>19.35729702719751</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>-1</v>
+        <v>-5.01</v>
       </c>
       <c r="L12" t="n">
-        <v>3.26</v>
+        <v>6.02</v>
       </c>
       <c r="M12" t="n">
         <v>0.25</v>
       </c>
       <c r="N12" t="n">
-        <v>2.84</v>
+        <v>4.05</v>
       </c>
       <c r="O12" t="n">
         <v>0.5</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>12.86</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H13" t="n">
-        <v>16.25</v>
+        <v>18</v>
       </c>
       <c r="I13" t="n">
         <v>16.88185816684314</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K13" t="n">
-        <v>14.25</v>
+        <v>5.01</v>
       </c>
       <c r="L13" t="n">
         <v>6.33</v>
@@ -1182,7 +1337,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>10.13</v>
+        <v>10.77</v>
       </c>
       <c r="O13" t="n">
         <v>-4.05</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>17.64</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44722</v>
+        <v>44725</v>
       </c>
       <c r="H14" t="n">
-        <v>16.2</v>
+        <v>15.65</v>
       </c>
       <c r="I14" t="n">
         <v>15.85495039637135</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K14" t="n">
-        <v>-10</v>
+        <v>-13.06</v>
       </c>
       <c r="L14" t="n">
         <v>13.89</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.35</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44747</v>
+        <v>44748</v>
       </c>
       <c r="H15" t="n">
-        <v>15.55</v>
+        <v>16.25</v>
       </c>
       <c r="I15" t="n">
         <v>15.86657279037151</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K15" t="n">
-        <v>0.64</v>
+        <v>-3.83</v>
       </c>
       <c r="L15" t="n">
         <v>4.79</v>
@@ -1296,7 +1475,7 @@
         <v>2.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.43</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
         <v>-3.4</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>13.19</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H16" t="n">
-        <v>29.35</v>
+        <v>27.25</v>
       </c>
       <c r="I16" t="n">
         <v>28.59473021706495</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K16" t="n">
-        <v>80.62</v>
+        <v>67.69</v>
       </c>
       <c r="L16" t="n">
         <v>3.38</v>
@@ -1353,7 +1544,7 @@
         <v>2.91</v>
       </c>
       <c r="N16" t="n">
-        <v>5.76</v>
+        <v>7.16</v>
       </c>
       <c r="O16" t="n">
         <v>4.5</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>21.74</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45019</v>
+        <v>45021</v>
       </c>
       <c r="H17" t="n">
-        <v>26.35</v>
+        <v>26.55</v>
       </c>
       <c r="I17" t="n">
         <v>26.40178309040757</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3</v>
+        <v>2.57</v>
       </c>
       <c r="L17" t="n">
         <v>14.68</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>12.77</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45226</v>
+        <v>45229</v>
       </c>
       <c r="H18" t="n">
-        <v>53.4</v>
+        <v>50.75</v>
       </c>
       <c r="I18" t="n">
         <v>52.1143663116807</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K18" t="n">
-        <v>101.13</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="L18" t="n">
         <v>2.26</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>17.92</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="H19" t="n">
-        <v>56.85</v>
+        <v>59.8</v>
       </c>
       <c r="I19" t="n">
         <v>58.64581275935784</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K19" t="n">
-        <v>-12.02</v>
+        <v>-17.83</v>
       </c>
       <c r="L19" t="n">
-        <v>16.85</v>
+        <v>19.11</v>
       </c>
       <c r="M19" t="n">
         <v>2.36</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>10.41</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45279</v>
+        <v>45280</v>
       </c>
       <c r="H20" t="n">
-        <v>59.7</v>
+        <v>55.8</v>
       </c>
       <c r="I20" t="n">
         <v>56.12603034879682</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.17</v>
+        <v>-6.69</v>
       </c>
       <c r="L20" t="n">
-        <v>4.77</v>
+        <v>7.19</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.81</v>
+        <v>6.53</v>
       </c>
       <c r="O20" t="n">
         <v>5.19</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>13.81</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="H21" t="n">
-        <v>50.8</v>
+        <v>51.1</v>
       </c>
       <c r="I21" t="n">
         <v>51.01228619581095</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K21" t="n">
-        <v>8.960000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="L21" t="n">
         <v>10.75</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>14.55</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45441</v>
+        <v>45442</v>
       </c>
       <c r="H22" t="n">
-        <v>50.45</v>
+        <v>49.05</v>
       </c>
       <c r="I22" t="n">
         <v>49.84606472904936</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.27</v>
+        <v>-4.01</v>
       </c>
       <c r="L22" t="n">
-        <v>2.74</v>
+        <v>4.31</v>
       </c>
       <c r="M22" t="n">
         <v>5.94</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>11.92</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="H23" t="n">
-        <v>33.54</v>
+        <v>35.84</v>
       </c>
       <c r="I23" t="n">
         <v>35.64239797096348</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K23" t="n">
-        <v>31.62</v>
+        <v>26.93</v>
       </c>
       <c r="L23" t="n">
         <v>6.01</v>
@@ -1752,7 +2027,7 @@
         <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>5.09</v>
+        <v>6.86</v>
       </c>
       <c r="O23" t="n">
         <v>-2.78</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>6</v>
+      </c>
+      <c r="U23" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>13.03</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H24" t="n">
-        <v>34.55</v>
+        <v>32.81</v>
       </c>
       <c r="I24" t="n">
         <v>33.46434761341538</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.6</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M24" t="n">
         <v>1.57</v>
       </c>
       <c r="N24" t="n">
-        <v>3.06</v>
+        <v>5.04</v>
       </c>
       <c r="O24" t="n">
         <v>6.86</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>12.65</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45687</v>
+        <v>45688</v>
       </c>
       <c r="H25" t="n">
-        <v>35.38</v>
+        <v>35.92</v>
       </c>
       <c r="I25" t="n">
         <v>35.43374537567693</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.83</v>
+        <v>-9.48</v>
       </c>
       <c r="L25" t="n">
-        <v>9.539999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>1.54</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>13.74</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45699</v>
+        <v>45700</v>
       </c>
       <c r="H26" t="n">
-        <v>35.28</v>
+        <v>34.4</v>
       </c>
       <c r="I26" t="n">
         <v>34.70350046085875</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.78</v>
+        <v>-4.23</v>
       </c>
       <c r="L26" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="M26" t="n">
         <v>1.96</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>16.1</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="H27" t="n">
-        <v>35.61</v>
+        <v>36.03</v>
       </c>
       <c r="I27" t="n">
         <v>35.80123565191199</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.52</v>
+        <v>-4.74</v>
       </c>
       <c r="L27" t="n">
-        <v>5.35</v>
+        <v>5.76</v>
       </c>
       <c r="M27" t="n">
         <v>1.65</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.12</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H28" t="n">
-        <v>45.71</v>
+        <v>43.32</v>
       </c>
       <c r="I28" t="n">
         <v>45.30233064845662</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K28" t="n">
-        <v>26.87</v>
+        <v>20.23</v>
       </c>
       <c r="L28" t="n">
         <v>8.74</v>
@@ -2037,7 +2372,7 @@
         <v>9.99</v>
       </c>
       <c r="N28" t="n">
-        <v>4.56</v>
+        <v>5.23</v>
       </c>
       <c r="O28" t="n">
         <v>1.18</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>12.89</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="H29" t="n">
-        <v>44.17</v>
+        <v>47.47</v>
       </c>
       <c r="I29" t="n">
         <v>45.96774622773276</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.96</v>
+        <v>-9.58</v>
       </c>
       <c r="L29" t="n">
-        <v>5.03</v>
+        <v>10.25</v>
       </c>
       <c r="M29" t="n">
         <v>1.99</v>
       </c>
       <c r="N29" t="n">
-        <v>3.76</v>
+        <v>7.47</v>
       </c>
       <c r="O29" t="n">
         <v>-5.23</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>12.36</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H30" t="n">
-        <v>57.28</v>
+        <v>54.26</v>
       </c>
       <c r="I30" t="n">
         <v>55.9362247346315</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K30" t="n">
-        <v>20.67</v>
+        <v>14.3</v>
       </c>
       <c r="L30" t="n">
         <v>7.63</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>7</v>
+      </c>
+      <c r="U30" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>16.57</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H31" t="n">
-        <v>56.43</v>
+        <v>58.44</v>
       </c>
       <c r="I31" t="n">
         <v>58.09032431236164</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K31" t="n">
-        <v>-4</v>
+        <v>-7.7</v>
       </c>
       <c r="L31" t="n">
-        <v>6.19</v>
+        <v>10.06</v>
       </c>
       <c r="M31" t="n">
-        <v>3.9</v>
+        <v>4.57</v>
       </c>
       <c r="N31" t="n">
         <v>8.49</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>14.48</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H32" t="n">
-        <v>57.25</v>
+        <v>56.77</v>
       </c>
       <c r="I32" t="n">
         <v>56.81789259046975</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.04</v>
+        <v>-2.86</v>
       </c>
       <c r="L32" t="n">
         <v>4.43</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>14.45</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="H33" t="n">
-        <v>56.75</v>
+        <v>58.62</v>
       </c>
       <c r="I33" t="n">
         <v>58.24059501853574</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K33" t="n">
-        <v>0.04</v>
+        <v>-3.26</v>
       </c>
       <c r="L33" t="n">
-        <v>2.91</v>
+        <v>4.81</v>
       </c>
       <c r="M33" t="n">
         <v>2.26</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.91</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H34" t="n">
-        <v>69.11</v>
+        <v>65.36</v>
       </c>
       <c r="I34" t="n">
         <v>66.2776633162206</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K34" t="n">
-        <v>17.89</v>
+        <v>11.5</v>
       </c>
       <c r="L34" t="n">
         <v>5.48</v>
@@ -2379,7 +2786,7 @@
         <v>2.15</v>
       </c>
       <c r="N34" t="n">
-        <v>3.23</v>
+        <v>5.43</v>
       </c>
       <c r="O34" t="n">
         <v>3.3</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2439,6 +2858,14 @@
       <c r="Q35" t="n">
         <v>39</v>
       </c>
+      <c r="R35" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5391,7 +5818,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72.3</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -5401,7 +5828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
@@ -5411,7 +5838,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8">
@@ -5421,7 +5848,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -5431,7 +5858,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -5441,7 +5868,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159.6</v>
+        <v>160.6</v>
       </c>
     </row>
     <row r="11">
@@ -5481,7 +5908,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11.17</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="15">
@@ -5491,7 +5918,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14.06</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -5501,7 +5928,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="17">
@@ -5511,7 +5938,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>101.13</v>
+        <v>91.15000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -5521,7 +5948,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="19">
@@ -5531,7 +5958,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="20">
@@ -5541,7 +5968,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.35</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="21">
@@ -5561,7 +5988,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -5571,7 +5998,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -5581,7 +6008,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="25">
@@ -5601,7 +6028,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.69</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="27">
@@ -5611,7 +6038,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.13</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="28">
@@ -5621,7 +6048,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
